--- a/data/env_test/case_excle/GovermentPurcharsZX/case_data_zz.xlsx
+++ b/data/env_test/case_excle/GovermentPurcharsZX/case_data_zz.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\interfaceAutomatic-main\data\env_test\case_excle\GovermentPurchars\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Lucas/PycharmProjects/InterfaceAutomaticTesttPlatform/data/env_test/case_excle/GovermentPurcharsZX/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{401E44B9-C578-400B-8FD0-AF9D940F72A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B591FD-4D41-EE4C-9002-C0EB2C661606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="20320" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="公开" sheetId="10" r:id="rId1"/>
@@ -548,10 +548,6 @@
     <t>b26</t>
   </si>
   <si>
-    <t>{"scaleProcess":2,"ifOfferRank":"false","ifWeight":"false","ifCreditScore":"false","scorePrincipleType":0,"reviewer":"1","methodName":"0","ifCreditWeight":"false","ifSupportPreviewSumScore":"true","scorePrincipleParam":"{\"ruleContent\":\"汇总全部评分后，计算评分均值\"}","creditScoreParam":"{}","tfId":"${tfId}","steps":[{"ifPqr":"true","ifSummarize":"false","ifReject":"false","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"资格评审","sort":1,"stepType":0,"items":[{"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"rejectCondition\":{\"ruleContent\":\"当不满足条款数据大于等于1时，并且被评委否决人数大于等于1名时，否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":null,\"rank\":null},\"rejectType\":1}"},{"ifPqr":"false","ifSummarize":0,"ifReject":"true","ifBlindBid":"true","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"技术审查","sort":2,"stepType":1,"items":[{"itemMinScore":11,"itemMaxScore":70,"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"weight\":100,\"standardScore\":70,\"ifSummarize\":0,\"rejectCondition\":{\"ruleContent\":\"汇总得分至少为30分，否则否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":30,\"rank\":null},\"rejectType\":1,\"ifReject\":1}","standardScore":70,"catalogId":""},{"ifPqr":"false","ifSummarize":"false","ifReject":"true","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"报价得分","sort":3,"stepType":2,"standardScore":30,"catalogId":"${catalogId}","stepParam":"{\"weight\":100,\"standardScore\":30,\"catalogId\":\"1887306232988766210\",\"ifOpenComputeChange\":0,\"standardPriceRule\":{\"computeMode\":2,\"computeFunType\":1,\"ruleContent\":\"系统将使用有效投标单位投标报价最低的报价为基准价。\"},\"quotationScoreRule\":{\"deductPointByHigh\":3,\"deductPointByLow\":3,\"deductPointTo\":0,\"computeFunType\":3,\"ruleContent\":\"以基准值为最高分Fmax，报价每高于基准报价1%时扣3分，报价每低于基准报价1%扣3分，最低扣至0分\"}}"}],"resultGatherModeParam":"{\"type\":1,\"recCandidateNum\":3,\"ruleContent\":\"以汇总得分由高到低依次推荐3名中标候选人。汇总得分相等时，投标报价低的优先；投标报价也相等的，技术得分高的优先；当技术得分也相等的，排名相同，最终汇总得分排名第一的确定为中标人。\"}","resultGatherModeDesc":"汇总得分 =  价格得分"}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>etbtrade/tpPurchaseGov?submit=true</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -573,6 +569,10 @@
   </si>
   <si>
     <t>{"paName":"","paCode":"","pqrMode":"${pqrMode}","ifIn":"false","ifRequiredTender":"true","ifPpp":"false","ifEEvaluation":"true","ifReserveField":"false","ifPushProvincePsp":"true","ifPushChinaPublicService":"true","tenderOrganizeForm":"${tenderOrganizeForm}","purchaseOrganizeForm":"2","inviteType":"${inviteType}","budgetDepartmentUnitType":"1","typeAttachment":[],"priceFrom":"1","priceDiscountRate":"","purchaseProjectName":"政采-${purchaseProjectName}","regionCodeShowCus":["13","1302","130203"],"regionCodeShow":"13-1301-130102","regionCode":"130102","regionName":"河北省-石家庄市-长安区","purchasePlanCode":"457484584501","unitBudget":"1","budget":"2344","affiliatedCompanyCus":"测试自动化专用企业","industriesTypeCus":["D","D44"],"industriesType":"D-D44","industriesTypeName":"电力、热力、燃气及水生产和供应业-电力、热力生产和供应业","purchaseProjectType":"${purchaseProjectType}","purchaseMode":"${purchaseMode}","purchaseContent":"测试","purchaserLxr":"测试","purchaserLxrTelephone":"13000000001","superviseUnitName":"监管人","superviseUnitCode":"931100000Y8C6DR0XT","transactionCenter":"无极金融服务平台交易中心","transactionCenterCode":"13012","transactionCenterCus":["13012"],"sectionList":[{"bidSectionDesc":"政采-${purchaseProjectName}-标段01","bidderCondition":"政采-${purchaseProjectName}-标段01","ifSignUpApprove":"false","bidSectionName":"政采-${purchaseProjectName}-标段01","classifyCodeCus":["B","B02","B0201","B020102"],"classifyCode":"B-B02-B0201-B020102","investBudget":"344","customId":"46241736127869061","bidSectionCode":"-","classifyName":"货物类-医疗器械-医疗器械-注射穿刺器械"},{"bidSectionDesc":"政采-${purchaseProjectName}-标段02","bidderCondition":"政采-${purchaseProjectName}-标段02","ifSignUpApprove":"false","bidSectionName":"政采-${purchaseProjectName}-标段02","classifyCodeCus":["B","B03","B0303","B030302"],"classifyCode":"B-B03-B0303-B030302","investBudget":"544","customId":"79531736127886926","bidSectionCode":"-","classifyName":"货物类-金属材料-合金-有色金属合金"}],"investCodeType":"2","affiliatedCompany":"测试自动化专用企业"}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"scaleProcess":2,"ifOfferRank":"false","ifWeight":"false","ifCreditScore":"false","scorePrincipleType":0,"reviewer":"1","methodName":"0","ifCreditWeight":"false","ifSupportPreviewSumScore":"true","scorePrincipleParam":"{\"ruleContent\":\"汇总全部评分后，计算评分均值\"}","creditScoreParam":"{}","tfId":"${tfId}","steps":[{"ifPqr":"true","ifSummarize":"false","ifReject":"false","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"资格评审","sort":1,"stepType":0,"items":[{"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"rejectCondition\":{\"ruleContent\":\"当不满足条款数据大于等于1时，并且被评委否决人数大于等于1名时，否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":null,\"rank\":null},\"rejectType\":1}"},{"ifPqr":"false","ifSummarize":0,"ifReject":"true","ifBlindBid":"true","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"技术审查","sort":2,"stepType":1,"items":[{"itemMinScore":11,"itemMaxScore":70,"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"weight\":100,\"standardScore\":70,\"ifSummarize\":0,\"rejectCondition\":{\"ruleContent\":\"汇总得分至少为30分，否则否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":30,\"rank\":null},\"rejectType\":1,\"ifReject\":1}","standardScore":70,"catalogId":""},{"ifPqr":"false","ifSummarize":"false","ifReject":"true","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"报价得分","sort":3,"stepType":2,"standardScore":30,"catalogId":"${catalogId}","stepParam":"{\"weight\":100,\"standardScore\":30,\"catalogId\":\"${catalogId}\",\"ifOpenComputeChange\":0,\"standardPriceRule\":{\"computeMode\":2,\"computeFunType\":1,\"ruleContent\":\"系统将使用有效投标单位投标报价最低的报价为基准价。\"},\"quotationScoreRule\":{\"deductPointByHigh\":3,\"deductPointByLow\":3,\"deductPointTo\":0,\"computeFunType\":3,\"ruleContent\":\"以基准值为最高分Fmax，报价每高于基准报价1%时扣3分，报价每低于基准报价1%扣3分，最低扣至0分\"}}"}],"resultGatherModeParam":"{\"type\":1,\"recCandidateNum\":3,\"ruleContent\":\"以汇总得分由高到低依次推荐3名中标候选人。汇总得分相等时，投标报价低的优先；投标报价也相等的，技术得分高的优先；当技术得分也相等的，排名相同，最终汇总得分排名第一的确定为中标人。\"}","resultGatherModeDesc":"汇总得分 =  价格得分"}</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -580,7 +580,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -631,6 +631,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1155,24 +1156,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="16.375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="45" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.375" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="2" customWidth="1"/>
+    <col min="7" max="8" width="11.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="53" style="2" customWidth="1"/>
-    <col min="11" max="11" width="26.125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="26.1640625" style="2" customWidth="1"/>
     <col min="12" max="12" width="35" style="2" customWidth="1"/>
-    <col min="13" max="13" width="45.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="45.6640625" style="2" customWidth="1"/>
     <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="18">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1216,7 +1217,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1245,7 +1246,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -1256,7 +1257,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>15</v>
@@ -1268,7 +1269,7 @@
         <v>17</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>46</v>
@@ -1277,7 +1278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>61</v>
       </c>
@@ -1288,7 +1289,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>15</v>
@@ -1309,7 +1310,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>62</v>
       </c>
@@ -1338,7 +1339,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>63</v>
       </c>
@@ -1367,7 +1368,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>64</v>
       </c>
@@ -1378,7 +1379,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>15</v>
@@ -1399,7 +1400,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="346.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="360">
       <c r="A8" s="1" t="s">
         <v>65</v>
       </c>
@@ -1432,7 +1433,7 @@
       </c>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="126">
       <c r="A9" s="1" t="s">
         <v>98</v>
       </c>
@@ -1463,7 +1464,7 @@
       </c>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="90">
       <c r="A10" s="1" t="s">
         <v>99</v>
       </c>
@@ -1497,7 +1498,7 @@
       </c>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="409.6">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -1526,7 +1527,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="247.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="252">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -1561,7 +1562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="90">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
@@ -1590,7 +1591,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="90">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
@@ -1619,7 +1620,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="90">
       <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
@@ -1648,7 +1649,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="90">
       <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
@@ -1677,7 +1678,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="90">
       <c r="A17" s="1" t="s">
         <v>37</v>
       </c>
@@ -1706,7 +1707,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="90">
       <c r="A18" s="1" t="s">
         <v>38</v>
       </c>
@@ -1735,7 +1736,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="90">
       <c r="A19" s="1" t="s">
         <v>39</v>
       </c>
@@ -1764,7 +1765,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
@@ -1793,7 +1794,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="409.6">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -1816,13 +1817,13 @@
         <v>17</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M21" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="90">
       <c r="A22" s="1" t="s">
         <v>110</v>
       </c>
@@ -1857,7 +1858,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>111</v>
       </c>
@@ -1889,7 +1890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="90">
       <c r="A24" s="1" t="s">
         <v>42</v>
       </c>
@@ -1921,19 +1922,19 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E2:E24">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
       <formula>"P4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
       <formula>"P3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
       <formula>"P2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1963,24 +1964,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3DF6D78-2EA9-0D4D-A8F7-EC937ACEC0C7}">
   <dimension ref="A1:N27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="16.375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="45" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.375" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="2" customWidth="1"/>
+    <col min="7" max="8" width="11.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="53" style="2" customWidth="1"/>
-    <col min="11" max="11" width="26.125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="26.1640625" style="2" customWidth="1"/>
     <col min="12" max="12" width="35" style="2" customWidth="1"/>
-    <col min="13" max="13" width="45.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="45.6640625" style="2" customWidth="1"/>
     <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="18">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2024,7 +2025,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>127</v>
       </c>
@@ -2053,7 +2054,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>128</v>
       </c>
@@ -2064,7 +2065,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>15</v>
@@ -2076,7 +2077,7 @@
         <v>17</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>46</v>
@@ -2085,7 +2086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>129</v>
       </c>
@@ -2096,7 +2097,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>15</v>
@@ -2117,7 +2118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>130</v>
       </c>
@@ -2146,7 +2147,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>131</v>
       </c>
@@ -2175,7 +2176,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>132</v>
       </c>
@@ -2186,7 +2187,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>15</v>
@@ -2207,7 +2208,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="346.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="360">
       <c r="A8" s="1" t="s">
         <v>133</v>
       </c>
@@ -2240,7 +2241,7 @@
       </c>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="126">
       <c r="A9" s="1" t="s">
         <v>134</v>
       </c>
@@ -2271,7 +2272,7 @@
       </c>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="90">
       <c r="A10" s="1" t="s">
         <v>135</v>
       </c>
@@ -2305,7 +2306,7 @@
       </c>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="409.6">
       <c r="A11" s="1" t="s">
         <v>136</v>
       </c>
@@ -2334,7 +2335,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="247.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="252">
       <c r="A12" s="1" t="s">
         <v>137</v>
       </c>
@@ -2369,7 +2370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="90">
       <c r="A13" s="1" t="s">
         <v>138</v>
       </c>
@@ -2398,7 +2399,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="90">
       <c r="A14" s="1" t="s">
         <v>139</v>
       </c>
@@ -2427,7 +2428,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="90">
       <c r="A15" s="1" t="s">
         <v>140</v>
       </c>
@@ -2456,7 +2457,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="90">
       <c r="A16" s="1" t="s">
         <v>141</v>
       </c>
@@ -2485,7 +2486,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="90">
       <c r="A17" s="1" t="s">
         <v>142</v>
       </c>
@@ -2514,7 +2515,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="90">
       <c r="A18" s="1" t="s">
         <v>143</v>
       </c>
@@ -2543,7 +2544,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="90">
       <c r="A19" s="1" t="s">
         <v>144</v>
       </c>
@@ -2572,7 +2573,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>145</v>
       </c>
@@ -2601,7 +2602,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="409.6">
       <c r="A21" s="1" t="s">
         <v>146</v>
       </c>
@@ -2630,7 +2631,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="90">
       <c r="A22" s="1" t="s">
         <v>147</v>
       </c>
@@ -2665,7 +2666,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>148</v>
       </c>
@@ -2697,7 +2698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>149</v>
       </c>
@@ -2720,13 +2721,13 @@
         <v>17</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M24" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="90">
       <c r="A25" s="1" t="s">
         <v>150</v>
       </c>
@@ -2761,7 +2762,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>151</v>
       </c>
@@ -2793,7 +2794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="90">
       <c r="A27" s="1" t="s">
         <v>152</v>
       </c>
@@ -2825,19 +2826,19 @@
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="E2:E27">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"P4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"P3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
       <formula>"P2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2867,24 +2868,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89098C1A-F74A-A24B-BCE4-B3BC9F558B9F}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="16.375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="45" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.375" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="2" customWidth="1"/>
+    <col min="7" max="8" width="11.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="53" style="2" customWidth="1"/>
-    <col min="11" max="11" width="26.125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="26.1640625" style="2" customWidth="1"/>
     <col min="12" max="12" width="35" style="2" customWidth="1"/>
-    <col min="13" max="13" width="45.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="45.6640625" style="2" customWidth="1"/>
     <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="18">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2928,7 +2929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -2957,7 +2958,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -2968,7 +2969,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>15</v>
@@ -2980,7 +2981,7 @@
         <v>17</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>46</v>
@@ -2989,7 +2990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>61</v>
       </c>
@@ -3000,7 +3001,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>15</v>
@@ -3021,7 +3022,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>62</v>
       </c>
@@ -3050,7 +3051,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>63</v>
       </c>
@@ -3079,7 +3080,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>64</v>
       </c>
@@ -3090,7 +3091,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>15</v>
@@ -3111,7 +3112,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="346.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="360">
       <c r="A8" s="1" t="s">
         <v>65</v>
       </c>
@@ -3144,7 +3145,7 @@
       </c>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="126">
       <c r="A9" s="1" t="s">
         <v>98</v>
       </c>
@@ -3166,7 +3167,7 @@
       <c r="H9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="10" t="s">
         <v>69</v>
       </c>
       <c r="K9" s="6"/>
@@ -3175,7 +3176,7 @@
       </c>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="90">
       <c r="A10" s="1" t="s">
         <v>99</v>
       </c>
@@ -3209,7 +3210,7 @@
       </c>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="409.6">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -3231,14 +3232,14 @@
       <c r="H11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>153</v>
+      <c r="J11" s="10" t="s">
+        <v>159</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="247.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="252">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -3273,7 +3274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="90">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
@@ -3302,7 +3303,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="90">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
@@ -3331,7 +3332,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="90">
       <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
@@ -3360,7 +3361,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="90">
       <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
@@ -3389,7 +3390,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="90">
       <c r="A17" s="1" t="s">
         <v>37</v>
       </c>
@@ -3418,7 +3419,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="90">
       <c r="A18" s="1" t="s">
         <v>38</v>
       </c>
@@ -3447,7 +3448,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="90">
       <c r="A19" s="1" t="s">
         <v>39</v>
       </c>
@@ -3476,7 +3477,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
@@ -3505,7 +3506,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="409.6">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -3528,13 +3529,13 @@
         <v>17</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M21" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="90">
       <c r="A22" s="1" t="s">
         <v>110</v>
       </c>
@@ -3569,7 +3570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>111</v>
       </c>
@@ -3601,7 +3602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="90">
       <c r="A24" s="1" t="s">
         <v>42</v>
       </c>
@@ -3633,19 +3634,19 @@
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="E2:E24">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"P4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"P3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"P2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
